--- a/results/Prelim result_Bignon.xlsx
+++ b/results/Prelim result_Bignon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elysialuo/Circadian-Transcriptomics/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B112133E-2DC7-1B47-B898-F7F46BE4EEAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D233EF0-AF50-EF4B-A04B-14F85E743CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{12245840-61EE-864C-9A7C-C81EB48CF35A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="7">
   <si>
     <t>Decrease</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Without RUV</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -12076,6 +12079,50 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>313580</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>31358</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>705555</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>10452</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Picture 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{542337FF-7439-C082-0EAD-C4C94F93D2F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11947407" y="2477284"/>
+          <a:ext cx="5377901" cy="5890082"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -12562,6 +12609,9 @@
       <c r="D29" t="s">
         <v>2</v>
       </c>
+      <c r="I29" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
